--- a/TRPV_sem_outliers.xlsx
+++ b/TRPV_sem_outliers.xlsx
@@ -431,28 +431,34 @@
         </is>
       </c>
       <c r="C2">
-        <v>42.36133333333333</v>
+        <v>24.0148</v>
       </c>
       <c r="D2">
-        <v>72.22199999999999</v>
+        <v>28.57316666666667</v>
       </c>
       <c r="E2">
-        <v>53.846</v>
+        <v>25.2685</v>
       </c>
       <c r="F2">
-        <v>58.3335</v>
-      </c>
-      <c r="G2">
-        <v>52.778</v>
+        <v>31.60025</v>
       </c>
       <c r="H2">
-        <v>54.545</v>
+        <v>19.6816</v>
+      </c>
+      <c r="I2">
+        <v>17.6284</v>
       </c>
       <c r="J2">
-        <v>69.18925</v>
+        <v>21.12366666666667</v>
+      </c>
+      <c r="K2">
+        <v>18.7084</v>
       </c>
       <c r="L2">
-        <v>44.444</v>
+        <v>24.16925</v>
+      </c>
+      <c r="M2">
+        <v>22.577</v>
       </c>
     </row>
     <row r="3">
@@ -508,34 +514,37 @@
         </is>
       </c>
       <c r="C4">
-        <v>34.23139999999999</v>
+        <v>23.99875</v>
       </c>
       <c r="D4">
-        <v>22.115</v>
+        <v>45.9582</v>
       </c>
       <c r="E4">
-        <v>42.86733333333333</v>
+        <v>38.9976</v>
       </c>
       <c r="F4">
-        <v>52.54366666666667</v>
+        <v>32.9414</v>
       </c>
       <c r="G4">
-        <v>50.64675</v>
+        <v>37.41583333333333</v>
       </c>
       <c r="H4">
-        <v>82.42449999999999</v>
+        <v>33.798</v>
       </c>
       <c r="I4">
-        <v>30.54366666666667</v>
+        <v>25.03766666666667</v>
       </c>
       <c r="J4">
-        <v>20.88566666666667</v>
+        <v>36.244</v>
       </c>
       <c r="K4">
-        <v>68.29300000000001</v>
+        <v>27.30933333333333</v>
       </c>
       <c r="L4">
-        <v>41.2815</v>
+        <v>52.97616666666666</v>
+      </c>
+      <c r="M4">
+        <v>35.12416666666667</v>
       </c>
     </row>
     <row r="5">
@@ -548,34 +557,37 @@
         </is>
       </c>
       <c r="C5">
-        <v>68.10533333333333</v>
+        <v>30.838</v>
       </c>
       <c r="D5">
-        <v>30.74366666666667</v>
+        <v>14.583</v>
       </c>
       <c r="E5">
-        <v>22.3062</v>
+        <v>22.4175</v>
       </c>
       <c r="F5">
-        <v>20.393</v>
+        <v>20.8584</v>
       </c>
       <c r="G5">
-        <v>36.31225</v>
+        <v>29.913</v>
       </c>
       <c r="H5">
-        <v>18.919</v>
+        <v>17.9468</v>
       </c>
       <c r="I5">
-        <v>45.215</v>
+        <v>25.5566</v>
       </c>
       <c r="J5">
-        <v>25.472</v>
+        <v>26.0652</v>
+      </c>
+      <c r="K5">
+        <v>31.053</v>
       </c>
       <c r="L5">
-        <v>93.6465</v>
+        <v>29.78766666666667</v>
       </c>
       <c r="M5">
-        <v>34.24233333333333</v>
+        <v>18.33233333333333</v>
       </c>
     </row>
     <row r="6">
@@ -674,34 +686,37 @@
         </is>
       </c>
       <c r="C8">
-        <v>43.06019999999999</v>
+        <v>33.333</v>
+      </c>
+      <c r="D8">
+        <v>68.8095</v>
       </c>
       <c r="E8">
-        <v>68.29300000000001</v>
+        <v>32.4385</v>
       </c>
       <c r="F8">
-        <v>78.99299999999999</v>
+        <v>82.99900000000001</v>
       </c>
       <c r="G8">
-        <v>79.10766666666667</v>
+        <v>70.58799999999999</v>
       </c>
       <c r="H8">
-        <v>53.125</v>
+        <v>41.51633333333334</v>
       </c>
       <c r="I8">
-        <v>52.7298</v>
+        <v>53.529</v>
       </c>
       <c r="J8">
-        <v>96.8245</v>
+        <v>77.22819999999999</v>
       </c>
       <c r="K8">
-        <v>39.759</v>
+        <v>76.44083333333333</v>
       </c>
       <c r="L8">
-        <v>72.47433333333333</v>
+        <v>85.5916</v>
       </c>
       <c r="M8">
-        <v>68.50649999999999</v>
+        <v>41.667</v>
       </c>
     </row>
     <row r="9">
@@ -714,34 +729,37 @@
         </is>
       </c>
       <c r="C9">
-        <v>29.3915</v>
+        <v>51.163</v>
       </c>
       <c r="D9">
-        <v>49.4185</v>
+        <v>79.91499999999999</v>
+      </c>
+      <c r="E9">
+        <v>85.58333333333333</v>
       </c>
       <c r="F9">
-        <v>47.7</v>
+        <v>56.22383333333334</v>
       </c>
       <c r="G9">
-        <v>42.9345</v>
+        <v>61.7002</v>
       </c>
       <c r="H9">
-        <v>61.0975</v>
+        <v>84.0805</v>
       </c>
       <c r="I9">
-        <v>48.7666</v>
+        <v>72.80133333333333</v>
       </c>
       <c r="J9">
-        <v>53.7425</v>
+        <v>43.79683333333333</v>
       </c>
       <c r="K9">
-        <v>59.0305</v>
+        <v>49.78733333333333</v>
       </c>
       <c r="L9">
-        <v>48.31939999999999</v>
+        <v>68.18340000000001</v>
       </c>
       <c r="M9">
-        <v>37.918</v>
+        <v>64.0898</v>
       </c>
     </row>
     <row r="10">
@@ -883,31 +901,37 @@
         </is>
       </c>
       <c r="C13">
-        <v>54.91466666666667</v>
+        <v>35.88039999999999</v>
+      </c>
+      <c r="D13">
+        <v>30.5965</v>
       </c>
       <c r="E13">
-        <v>67.3565</v>
+        <v>36.7334</v>
+      </c>
+      <c r="F13">
+        <v>43.65466666666666</v>
       </c>
       <c r="G13">
-        <v>84.8485</v>
+        <v>29.1028</v>
       </c>
       <c r="H13">
-        <v>34.375</v>
+        <v>27.08233333333333</v>
       </c>
       <c r="I13">
-        <v>31.915</v>
+        <v>34.7942</v>
       </c>
       <c r="J13">
-        <v>28.804</v>
+        <v>32.3265</v>
       </c>
       <c r="K13">
-        <v>30.909</v>
+        <v>28.1582</v>
       </c>
       <c r="L13">
-        <v>54.4405</v>
+        <v>33.3796</v>
       </c>
       <c r="M13">
-        <v>37.1055</v>
+        <v>32.3275</v>
       </c>
     </row>
     <row r="14">
@@ -963,37 +987,37 @@
         </is>
       </c>
       <c r="C15">
-        <v>21.4486</v>
+        <v>33.0705</v>
       </c>
       <c r="D15">
-        <v>25.7985</v>
+        <v>70.11499999999999</v>
       </c>
       <c r="E15">
-        <v>23.30433333333333</v>
+        <v>85.01220000000001</v>
       </c>
       <c r="F15">
-        <v>24.445</v>
+        <v>85.5655</v>
       </c>
       <c r="G15">
-        <v>26.6906</v>
+        <v>96.4828</v>
       </c>
       <c r="H15">
-        <v>28.349</v>
+        <v>64.742</v>
       </c>
       <c r="I15">
-        <v>34.3654</v>
+        <v>78.357</v>
       </c>
       <c r="J15">
-        <v>33.6894</v>
+        <v>75.61499999999999</v>
       </c>
       <c r="K15">
-        <v>33.24566666666666</v>
+        <v>87.5408</v>
       </c>
       <c r="L15">
-        <v>25.90383333333333</v>
+        <v>85.70925</v>
       </c>
       <c r="M15">
-        <v>49.40199999999999</v>
+        <v>93.5352</v>
       </c>
     </row>
     <row r="16">
@@ -1048,6 +1072,39 @@
           <t>GAG</t>
         </is>
       </c>
+      <c r="C17">
+        <v>53.10525</v>
+      </c>
+      <c r="D17">
+        <v>75.95439999999999</v>
+      </c>
+      <c r="E17">
+        <v>64.86120000000001</v>
+      </c>
+      <c r="F17">
+        <v>66.48083333333334</v>
+      </c>
+      <c r="G17">
+        <v>64.64566666666667</v>
+      </c>
+      <c r="H17">
+        <v>76.32680000000001</v>
+      </c>
+      <c r="I17">
+        <v>71.29116666666667</v>
+      </c>
+      <c r="J17">
+        <v>71.783</v>
+      </c>
+      <c r="K17">
+        <v>78.179</v>
+      </c>
+      <c r="L17">
+        <v>61.0865</v>
+      </c>
+      <c r="M17">
+        <v>68.8472</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18">
@@ -1460,6 +1517,9 @@
       <c r="H27">
         <v>32.1976</v>
       </c>
+      <c r="I27">
+        <v>25.70425</v>
+      </c>
       <c r="J27">
         <v>40.407</v>
       </c>
@@ -1996,37 +2056,31 @@
         </is>
       </c>
       <c r="C40">
-        <v>43.94125</v>
+        <v>58.851</v>
       </c>
       <c r="D40">
-        <v>60.56140000000001</v>
+        <v>47.82866666666666</v>
       </c>
       <c r="E40">
-        <v>46.512</v>
+        <v>42.10433333333334</v>
       </c>
       <c r="F40">
-        <v>65.7865</v>
+        <v>40.9342</v>
       </c>
       <c r="G40">
-        <v>40.0395</v>
+        <v>28.03583333333333</v>
       </c>
       <c r="H40">
-        <v>64.1876</v>
-      </c>
-      <c r="I40">
-        <v>60.59533333333334</v>
+        <v>23.26883333333333</v>
       </c>
       <c r="J40">
-        <v>67.762</v>
-      </c>
-      <c r="K40">
-        <v>72.94833333333334</v>
+        <v>25.5775</v>
       </c>
       <c r="L40">
-        <v>33.904</v>
+        <v>20.90283333333333</v>
       </c>
       <c r="M40">
-        <v>53.33733333333333</v>
+        <v>21.957</v>
       </c>
     </row>
     <row r="41">
